--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_10.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.035196130472079</v>
+        <v>0.02717477444291556</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00845820783045732</v>
+        <v>0.008445755456178603</v>
       </c>
       <c r="C2" t="n">
-        <v>63129780</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63129780</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>41117686</v>
+        <v>3862323</v>
       </c>
       <c r="L2" t="n">
-        <v>20892353</v>
+        <v>1819316</v>
       </c>
       <c r="M2" t="n">
-        <v>4545507</v>
+        <v>367376</v>
       </c>
       <c r="N2" t="n">
-        <v>139975</v>
+        <v>10254</v>
       </c>
       <c r="O2" t="n">
-        <v>2778525</v>
+        <v>229797</v>
       </c>
       <c r="P2" t="n">
-        <v>1105183</v>
+        <v>93001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999954104423523</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.803433895111084</v>
+        <v>0.7496104836463928</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6289739012718201</v>
+        <v>0.5447162985801697</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5333747863769531</v>
+        <v>0.4299903213977814</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1436650305986404</v>
+        <v>0.1062700822949409</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5917494297027588</v>
+        <v>0.4891243875026703</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6994798183441162</v>
+        <v>0.5941075682640076</v>
       </c>
       <c r="X2" t="n">
-        <v>63129780</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63129780</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>47949558</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>29849211</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8017135</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>590732</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559409618377686</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116660952568054</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582287430763245</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617533564567566</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902009129524231</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.009426641412300702</v>
+        <v>0.006953781213440931</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002027664927559576</v>
+        <v>0.002023579242838846</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>41117686</v>
+        <v>3862323</v>
       </c>
       <c r="E3" t="n">
-        <v>8550126</v>
+        <v>1074181</v>
       </c>
       <c r="F3" t="n">
-        <v>341958</v>
+        <v>55935</v>
       </c>
       <c r="G3" t="n">
-        <v>26804</v>
+        <v>4181</v>
       </c>
       <c r="H3" t="n">
-        <v>35178</v>
+        <v>5746</v>
       </c>
       <c r="I3" t="n">
-        <v>3955</v>
+        <v>619</v>
       </c>
       <c r="J3" t="n">
-        <v>100165930</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>103160510</v>
+        <v>10122893</v>
       </c>
       <c r="L3" t="n">
-        <v>118162466</v>
+        <v>11566998</v>
       </c>
       <c r="M3" t="n">
-        <v>149966791</v>
+        <v>14986470</v>
       </c>
       <c r="N3" t="n">
-        <v>161568096</v>
+        <v>16239786</v>
       </c>
       <c r="O3" t="n">
-        <v>156278653</v>
+        <v>15664046</v>
       </c>
       <c r="P3" t="n">
-        <v>160886563</v>
+        <v>16158657</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8211098909378052</v>
+        <v>0.7720029354095459</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6367810368537903</v>
+        <v>0.5466062426567078</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4860177636146545</v>
+        <v>0.3897789418697357</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1566479802131653</v>
+        <v>0.1139611899852753</v>
       </c>
       <c r="V3" t="n">
-        <v>0.544762909412384</v>
+        <v>0.4488766193389893</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5712682604789734</v>
+        <v>0.4798689484596252</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47949558</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1972670</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>84826</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68106</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100166220</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111010280</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>127594505</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>152619092</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>162100491</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157696105</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>161228809</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575406908988953</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097784161567688</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85721355676651</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661096453666687</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014128446578979</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0764936784222492</v>
+        <v>0.06424244444140195</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03198836053224347</v>
+        <v>0.03194845442669837</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>9249469</v>
+        <v>1171374</v>
       </c>
       <c r="E4" t="n">
-        <v>20892353</v>
+        <v>1819316</v>
       </c>
       <c r="F4" t="n">
-        <v>2175434</v>
+        <v>262489</v>
       </c>
       <c r="G4" t="n">
-        <v>131494</v>
+        <v>18764</v>
       </c>
       <c r="H4" t="n">
-        <v>318178</v>
+        <v>49400</v>
       </c>
       <c r="I4" t="n">
-        <v>42388</v>
+        <v>7042</v>
       </c>
       <c r="J4" t="n">
-        <v>290</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>10059750</v>
+        <v>1290117</v>
       </c>
       <c r="L4" t="n">
-        <v>12324214</v>
+        <v>1520617</v>
       </c>
       <c r="M4" t="n">
-        <v>3976656</v>
+        <v>487006</v>
       </c>
       <c r="N4" t="n">
-        <v>834340</v>
+        <v>86236</v>
       </c>
       <c r="O4" t="n">
-        <v>1916917</v>
+        <v>240016</v>
       </c>
       <c r="P4" t="n">
-        <v>474824</v>
+        <v>63538</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999976754188538</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8121757507324219</v>
+        <v>0.7606419920921326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6328533887863159</v>
+        <v>0.545659601688385</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5085963010787964</v>
+        <v>0.4088983833789825</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1498758792877197</v>
+        <v>0.1099813431501389</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5672849416732788</v>
+        <v>0.4681369960308075</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6289060711860657</v>
+        <v>0.5309125185012817</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2063963</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>29849211</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>828823</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55262</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11381</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2209980</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2892175</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1324355</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>301945</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499465</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567400813102722</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107212424278259</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577207922935486</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614247560501099</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017109274864197</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>583966</v>
+        <v>88304</v>
       </c>
       <c r="E5" t="n">
-        <v>3012188</v>
+        <v>338728</v>
       </c>
       <c r="F5" t="n">
-        <v>4545507</v>
+        <v>367376</v>
       </c>
       <c r="G5" t="n">
-        <v>269407</v>
+        <v>27968</v>
       </c>
       <c r="H5" t="n">
-        <v>827191</v>
+        <v>103240</v>
       </c>
       <c r="I5" t="n">
-        <v>114276</v>
+        <v>16904</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8958054</v>
+        <v>1140667</v>
       </c>
       <c r="L5" t="n">
-        <v>11916967</v>
+        <v>1509069</v>
       </c>
       <c r="M5" t="n">
-        <v>4807046</v>
+        <v>575148</v>
       </c>
       <c r="N5" t="n">
-        <v>753589</v>
+        <v>79724</v>
       </c>
       <c r="O5" t="n">
-        <v>2321905</v>
+        <v>282141</v>
       </c>
       <c r="P5" t="n">
-        <v>829430</v>
+        <v>100804</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999982118606567</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8835378289222717</v>
+        <v>0.8519259095191956</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8515506982803345</v>
+        <v>0.8154430985450745</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9462099671363831</v>
+        <v>0.9352976083755493</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9902757406234741</v>
+        <v>0.9898903369903564</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9740421175956726</v>
+        <v>0.9681922197341919</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9920129179954529</v>
+        <v>0.9899889230728149</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80454</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>857060</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8017135</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>99758</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>291816</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2126182</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2960109</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1335418</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>302832</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502837</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734460115432739</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641615152359009</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837119579315186</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962964653968811</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938620328903198</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983729124069214</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>158926</v>
+        <v>18506</v>
       </c>
       <c r="E6" t="n">
-        <v>224432</v>
+        <v>24979</v>
       </c>
       <c r="F6" t="n">
-        <v>250525</v>
+        <v>22768</v>
       </c>
       <c r="G6" t="n">
-        <v>139975</v>
+        <v>10254</v>
       </c>
       <c r="H6" t="n">
-        <v>105369</v>
+        <v>11514</v>
       </c>
       <c r="I6" t="n">
-        <v>14273</v>
+        <v>1951</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65084</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53535</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109471</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>590732</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>69932</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>63157</v>
+        <v>11290</v>
       </c>
       <c r="E7" t="n">
-        <v>486357</v>
+        <v>74061</v>
       </c>
       <c r="F7" t="n">
-        <v>1102176</v>
+        <v>129438</v>
       </c>
       <c r="G7" t="n">
-        <v>370226</v>
+        <v>30329</v>
       </c>
       <c r="H7" t="n">
-        <v>2778525</v>
+        <v>229797</v>
       </c>
       <c r="I7" t="n">
-        <v>299932</v>
+        <v>37022</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8100</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297921</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76159</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>4232</v>
+        <v>643</v>
       </c>
       <c r="E8" t="n">
-        <v>51111</v>
+        <v>8668</v>
       </c>
       <c r="F8" t="n">
-        <v>106563</v>
+        <v>16376</v>
       </c>
       <c r="G8" t="n">
-        <v>36409</v>
+        <v>4994</v>
       </c>
       <c r="H8" t="n">
-        <v>631001</v>
+        <v>70116</v>
       </c>
       <c r="I8" t="n">
-        <v>1105183</v>
+        <v>93001</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
